--- a/GRO_data.xlsx
+++ b/GRO_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,116 +413,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Month_#</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Billability</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Utilization</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Adjusted UT</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Research hours</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Number of requests</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Canceled requests</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Effective requests</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Interim submissions</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Avg. hours per request</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Adj. Ack. SLA</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Due to DRS SLA</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Available Capacity</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>FTE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Total Surveys</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Positive Surveys</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Negative Surveys</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Positive feedback rate</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Negative feedback rate</t>
         </is>
@@ -578,10 +566,10 @@
         <v>0.2349137931034483</v>
       </c>
       <c r="M2" t="n">
-        <v>2.763020833333333</v>
+        <v>3.470744680851064</v>
       </c>
       <c r="N2" t="n">
-        <v>2.612676056338028</v>
+        <v>3.204225352112676</v>
       </c>
       <c r="O2" t="n">
         <v>1623.5</v>
@@ -650,10 +638,10 @@
         <v>0.2261029411764706</v>
       </c>
       <c r="M3" t="n">
-        <v>2.535796766743649</v>
+        <v>2.862790697674419</v>
       </c>
       <c r="N3" t="n">
-        <v>2.353061224489796</v>
+        <v>2.628571428571429</v>
       </c>
       <c r="O3" t="n">
         <v>1671.5</v>
@@ -722,10 +710,10 @@
         <v>0.2176991150442478</v>
       </c>
       <c r="M4" t="n">
-        <v>2.566739606126915</v>
+        <v>2.792035398230088</v>
       </c>
       <c r="N4" t="n">
-        <v>2.359315589353612</v>
+        <v>2.539923954372624</v>
       </c>
       <c r="O4" t="n">
         <v>2009.5</v>
@@ -1436,10 +1424,10 @@
         <v>0.196319018404908</v>
       </c>
       <c r="M14" t="n">
-        <v>2.520190023752969</v>
+        <v>3.159806295399516</v>
       </c>
       <c r="N14" t="n">
-        <v>2.403887688984881</v>
+        <v>2.948164146868251</v>
       </c>
       <c r="O14" t="n">
         <v>1929</v>
@@ -1506,10 +1494,10 @@
         <v>0.2165725047080979</v>
       </c>
       <c r="M15" t="n">
-        <v>2.614285714285714</v>
+        <v>2.952038369304556</v>
       </c>
       <c r="N15" t="n">
-        <v>2.417190775681342</v>
+        <v>2.70020964360587</v>
       </c>
       <c r="O15" t="n">
         <v>2139</v>
@@ -1578,10 +1566,10 @@
         <v>0.2</v>
       </c>
       <c r="M16" t="n">
-        <v>2.647855530474041</v>
+        <v>2.881278538812786</v>
       </c>
       <c r="N16" t="n">
-        <v>2.423828125</v>
+        <v>2.609375</v>
       </c>
       <c r="O16" t="n">
         <v>2156.5</v>
@@ -2290,10 +2278,10 @@
         <v>0.2724137931034483</v>
       </c>
       <c r="M26" t="n">
-        <v>4.457983193277311</v>
+        <v>5.673913043478261</v>
       </c>
       <c r="N26" t="n">
-        <v>3.975</v>
+        <v>4.875</v>
       </c>
       <c r="O26" t="n">
         <v>1375.1</v>
@@ -2360,10 +2348,10 @@
         <v>0.312280701754386</v>
       </c>
       <c r="M27" t="n">
-        <v>5.059907834101383</v>
+        <v>5.752336448598131</v>
       </c>
       <c r="N27" t="n">
-        <v>4.208029197080292</v>
+        <v>4.700729927007299</v>
       </c>
       <c r="O27" t="n">
         <v>1287.8</v>
@@ -2430,10 +2418,10 @@
         <v>0.3069306930693069</v>
       </c>
       <c r="M28" t="n">
-        <v>5.380733944954128</v>
+        <v>5.924882629107981</v>
       </c>
       <c r="N28" t="n">
-        <v>4.32404181184669</v>
+        <v>4.655052264808362</v>
       </c>
       <c r="O28" t="n">
         <v>1159.8</v>
@@ -3088,6 +3076,198 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.3174603174603175</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8796967331921063</v>
+      </c>
+      <c r="F38" t="n">
+        <v>789</v>
+      </c>
+      <c r="G38" t="n">
+        <v>270</v>
+      </c>
+      <c r="H38" t="n">
+        <v>10</v>
+      </c>
+      <c r="I38" t="n">
+        <v>260</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.01162790697674419</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.325925925925926</v>
+      </c>
+      <c r="M38" t="n">
+        <v>6.214285714285714</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O38" t="n">
+        <v>896.8999999999999</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>GRO</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.4453488372093024</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.148262208534976</v>
+      </c>
+      <c r="F39" t="n">
+        <v>522</v>
+      </c>
+      <c r="G39" t="n">
+        <v>142</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>137</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.01030927835051546</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="M39" t="n">
+        <v>15.98701298701299</v>
+      </c>
+      <c r="N39" t="n">
+        <v>9.401459854014599</v>
+      </c>
+      <c r="O39" t="n">
+        <v>454.6</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>GRO</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B40" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.2346723044397463</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.4934447485953032</v>
+      </c>
+      <c r="F40" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>101</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>98</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.3465346534653465</v>
+      </c>
+      <c r="M40" t="n">
+        <v>52.58333333333334</v>
+      </c>
+      <c r="N40" t="n">
+        <v>13.63265306122449</v>
+      </c>
+      <c r="O40" t="n">
+        <v>694.1</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>GRO</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
